--- a/comparison_report.xlsx
+++ b/comparison_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,11 +473,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AM377</t>
+          <t>AM360</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -491,33 +491,33 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>substantial</t>
+          <t>observant</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>substantial</t>
+          <t>observant</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>#C6EFCE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>#FFC7CE</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AN377</t>
+          <t>AN360</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -531,33 +531,33 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>substantive</t>
+          <t>observable</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>substantive</t>
+          <t>observable</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>#C6EFCE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>#FFC7CE</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AO377</t>
+          <t>AO360</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -571,342 +571,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Wrong</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>#C6EFCE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>#FFC7CE</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AG383</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>383</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Unnamed: 32</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>สีพื้นหลัง</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>perpetuity</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>perpetuity</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>#FFC7CE</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AG384</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>384</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Unnamed: 32</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>สีพื้นหลัง</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>systematization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>systematization</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>#FFC7CE</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AI387</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>387</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Unnamed: 34</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>สีพื้นหลัง</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>substantial</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>substantial</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>#FFC7CE</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AJ387</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>387</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Unnamed: 35</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>สีพื้นหลัง</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>substantially</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>substantially</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>#FFC7CE</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI388</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>388</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Unnamed: 34</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>สีพื้นหลัง</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>deliberative</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>deliberative</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>#FFC7CE</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AJ388</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>388</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Unnamed: 35</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>สีพื้นหลัง</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>deliberatively</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>deliberatively</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>#FFC7CE</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AG390</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>390</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Unnamed: 32</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>สีพื้นหลัง</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>exemplification</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>exemplification</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>#FFC7CE</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AG391</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>391</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Unnamed: 32</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>สีพื้นหลัง</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>legitimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>legitimization</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>#FFC7CE</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
         </is>
       </c>
     </row>

--- a/comparison_report.xlsx
+++ b/comparison_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,122 +473,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AM360</t>
+          <t>AP16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>360</v>
+        <v>16</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unnamed: 38</t>
+          <t>Unnamed: 41</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>สีพื้นหลัง</t>
+          <t>คอลัมน์เกิน (ไฟล์ 1)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>observant</t>
+          <t>test</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>observant</t>
+          <t>(ไม่มีคอลัมน์นี้)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>#C6EFCE</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>#FFC7CE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AN360</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>360</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Unnamed: 39</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>สีพื้นหลัง</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>observable</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>observable</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>#FFC7CE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AO360</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>360</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Unnamed: 40</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ค่า + สีพื้นหลัง</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Wrong</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>#C6EFCE</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>#FFC7CE</t>
-        </is>
-      </c>
+          <t>(ไม่มีสี)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparison_report.xlsx
+++ b/comparison_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,38 +473,158 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AP16</t>
+          <t>R372</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unnamed: 41</t>
+          <t>Part 4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>คอลัมน์เกิน (ไฟล์ 1)</t>
+          <t>สีพื้นหลัง</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>000477) cuss</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(ไม่มีคอลัมน์นี้)</t>
+          <t>000477) cuss</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>(ไม่มีสี)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>#C6EFCE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>#FFC7CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S372</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>372</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Unnamed: 18</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>สีพื้นหลัง</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>000477) cuss: informal or mea languages</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>000477) cuss: informal or mea languages</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>#C6EFCE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>#FFC7CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T372</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>372</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Unnamed: 19</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ค่า + สีพื้นหลัง</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Wrong</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>#C6EFCE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>#FFC7CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>U372</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>372</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Unnamed: 20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ค่า + สีพื้นหลัง</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>#C6EFCE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>#FFC7CE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
